--- a/Ass/Week3_Practice.xlsx
+++ b/Ass/Week3_Practice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jean\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jean\Documents\ComproT2\Ass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0558A09-6FE7-4779-9A46-39A0C514C91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A5F581-FC8C-471D-B558-0AD665C92051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{D436696A-4DAC-E846-B825-86D9F603EE54}"/>
   </bookViews>
@@ -166,15 +166,6 @@
     <t>Step 8 Path: [E1, D1, D2, D3, C3, B3, B2, B1]</t>
   </si>
   <si>
-    <t>Step 9 Path: [E1, D1, D2, D3, C3, B3, B2, B1]</t>
-  </si>
-  <si>
-    <t>Step 10 Path: [E1, D1, D2, D3, C3, B3, B2]</t>
-  </si>
-  <si>
-    <t>Step 11 Path: [E1, D1, D2, D3, C3, B3]</t>
-  </si>
-  <si>
     <t>Step 12 Path: [E1, D1, D2, D3, C3, B3]</t>
   </si>
   <si>
@@ -248,6 +239,15 @@
   </si>
   <si>
     <t>[86]</t>
+  </si>
+  <si>
+    <t>Step 9 Path: [E1, D1, D2, D3, C3, B3, B2, B1,A1]</t>
+  </si>
+  <si>
+    <t>Step 10 Path: [E1, D1, D2, D3, C3, B3, B2,B1]</t>
+  </si>
+  <si>
+    <t>Step 11 Path: [E1, D1, D2, D3, C3, B3,B2]</t>
   </si>
 </sst>
 </file>
@@ -1387,14 +1387,14 @@
         <v>13</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="6"/>
       <c r="E50" s="5"/>
       <c r="F50" s="8"/>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -1482,7 +1482,7 @@
       <c r="E56" s="5"/>
       <c r="F56" s="8"/>
       <c r="G56" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -1490,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>31</v>
@@ -1570,7 +1570,7 @@
       <c r="E62" s="5"/>
       <c r="F62" s="8"/>
       <c r="G62" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -1581,7 +1581,7 @@
         <v>33</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>31</v>
@@ -1658,7 +1658,7 @@
       <c r="E68" s="5"/>
       <c r="F68" s="8"/>
       <c r="G68" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -1746,7 +1746,7 @@
       <c r="E74" s="5"/>
       <c r="F74" s="8"/>
       <c r="G74" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F80" s="8"/>
       <c r="G80" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -1932,7 +1932,7 @@
         <v>31</v>
       </c>
       <c r="G86" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -2079,10 +2079,10 @@
         <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2090,10 +2090,10 @@
         <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2101,10 +2101,10 @@
         <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2115,7 +2115,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2123,10 +2123,10 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2134,10 +2134,10 @@
         <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2145,10 +2145,10 @@
         <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2156,10 +2156,10 @@
         <v>26</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2167,10 +2167,10 @@
         <v>27</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2181,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2189,10 +2189,10 @@
         <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2203,7 +2203,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2211,10 +2211,10 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2225,7 +2225,7 @@
         <v>5</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2259,10 +2259,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2270,10 +2270,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2281,10 +2281,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2292,10 +2292,10 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2306,7 +2306,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2317,7 +2317,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2328,7 +2328,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2339,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2350,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2358,10 +2358,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2372,7 +2372,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2380,10 +2380,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="21" x14ac:dyDescent="0.4">
@@ -2405,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
